--- a/docs/All-Tests.xlsx
+++ b/docs/All-Tests.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Sprint</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Kind</t>
+  </si>
+  <si>
+    <t>Framework</t>
   </si>
 </sst>
 </file>
@@ -212,6 +215,7 @@
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -242,6 +246,9 @@
       <c r="I1" t="s" s="1">
         <v>8</v>
       </c>
+      <c r="J1" t="s" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="5">
@@ -289,6 +296,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="5">
@@ -336,6 +348,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="5">
@@ -383,6 +400,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="5">
@@ -430,6 +452,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="5">
@@ -477,6 +504,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="5">
@@ -524,6 +556,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="5">
@@ -571,6 +608,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="5">
@@ -618,6 +660,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="5">
@@ -665,6 +712,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="5">
@@ -712,6 +764,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="5">
@@ -759,6 +816,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="5">
@@ -806,6 +868,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="5">
@@ -853,6 +920,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="5">
@@ -900,6 +972,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="8">
@@ -947,6 +1024,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="8">
@@ -994,6 +1076,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="8">
@@ -1041,6 +1128,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="8">
@@ -1088,6 +1180,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="8">
@@ -1135,6 +1232,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="8">
@@ -1182,6 +1284,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="8">
@@ -1229,6 +1336,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="8">
@@ -1276,6 +1388,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="8">
@@ -1323,6 +1440,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="8">
@@ -1370,6 +1492,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="6">
@@ -1417,6 +1544,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="6">
@@ -1464,6 +1596,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="6">
@@ -1511,6 +1648,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="6">
@@ -1558,6 +1700,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="6">
@@ -1605,6 +1752,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="6">
@@ -1652,6 +1804,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="6">
@@ -1699,6 +1856,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="6">
@@ -1746,6 +1908,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="6">
@@ -1793,6 +1960,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="6">
@@ -1840,6 +2012,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="6">
@@ -1887,6 +2064,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="6">
@@ -1934,6 +2116,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="6">
@@ -1981,6 +2168,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="6">
@@ -2028,6 +2220,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="6">
@@ -2075,6 +2272,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="6">
@@ -2122,6 +2324,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="6">
@@ -2169,6 +2376,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="6">
@@ -2216,6 +2428,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="6">
@@ -2263,6 +2480,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr" s="6">
@@ -2310,6 +2532,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="6">
@@ -2357,6 +2584,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="6">
@@ -2404,6 +2636,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="6">
@@ -2451,6 +2688,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="6">
@@ -2498,6 +2740,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="6">
@@ -2545,6 +2792,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="6">
@@ -2592,6 +2844,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr" s="5">
@@ -2639,6 +2896,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr" s="5">
@@ -2686,6 +2948,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr" s="5">
@@ -2733,6 +3000,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="5">
@@ -2780,6 +3052,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="5">
@@ -2827,6 +3104,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="5">
@@ -2874,6 +3156,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr" s="6">
@@ -2921,6 +3208,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="6">
@@ -2968,6 +3260,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="5">
@@ -3015,6 +3312,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="5">
@@ -3062,6 +3364,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="5">
@@ -3109,6 +3416,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="5">
@@ -3156,6 +3468,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="5">
@@ -3203,6 +3520,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="5">
@@ -3250,6 +3572,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="5">
@@ -3297,6 +3624,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="5">
@@ -3344,6 +3676,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="5">
@@ -3391,6 +3728,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="5">
@@ -3438,6 +3780,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="6">
@@ -3485,6 +3832,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="6">
@@ -3532,6 +3884,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="6">
@@ -3579,6 +3936,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="6">
@@ -3626,6 +3988,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="6">
@@ -3673,6 +4040,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="6">
@@ -3720,6 +4092,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="6">
@@ -3767,6 +4144,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="6">
@@ -3814,6 +4196,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr" s="6">
@@ -3861,6 +4248,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="6">
@@ -3908,6 +4300,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="6">
@@ -3955,6 +4352,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="6">
@@ -4002,6 +4404,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="6">
@@ -4049,6 +4456,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="6">
@@ -4096,6 +4508,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="6">
@@ -4143,6 +4560,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="6">
@@ -4190,6 +4612,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr" s="6">
@@ -4237,6 +4664,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr" s="6">
@@ -4284,6 +4716,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="6">
@@ -4331,6 +4768,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="6">
@@ -4378,6 +4820,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="6">
@@ -4425,6 +4872,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="6">
@@ -4472,6 +4924,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="6">
@@ -4519,6 +4976,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="6">
@@ -4566,6 +5028,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="6">
@@ -4613,6 +5080,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr" s="6">
@@ -4660,6 +5132,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr" s="6">
@@ -4707,6 +5184,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr" s="6">
@@ -4754,6 +5236,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr" s="6">
@@ -4801,6 +5288,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr" s="6">
@@ -4848,6 +5340,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr" s="6">
@@ -4895,6 +5392,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr" s="6">
@@ -4942,6 +5444,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr" s="6">
@@ -4989,6 +5496,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr" s="6">
@@ -5036,6 +5548,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr" s="6">
@@ -5083,6 +5600,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr" s="6">
@@ -5130,6 +5652,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr" s="6">
@@ -5177,6 +5704,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr" s="6">
@@ -5224,6 +5756,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr" s="6">
@@ -5271,6 +5808,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr" s="6">
@@ -5318,6 +5860,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr" s="6">
@@ -5365,6 +5912,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr" s="6">
@@ -5412,6 +5964,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr" s="6">
@@ -5459,6 +6016,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr" s="6">
@@ -5506,6 +6068,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr" s="6">
@@ -5553,6 +6120,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr" s="6">
@@ -5600,6 +6172,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr" s="6">
@@ -5647,6 +6224,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr" s="6">
@@ -5694,6 +6276,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr" s="6">
@@ -5741,6 +6328,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr" s="6">
@@ -5788,6 +6380,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr" s="6">
@@ -5835,6 +6432,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr" s="6">
@@ -5882,6 +6484,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr" s="6">
@@ -5929,6 +6536,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr" s="6">
@@ -5976,6 +6588,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr" s="6">
@@ -6023,6 +6640,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr" s="6">
@@ -6070,6 +6692,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr" s="6">
@@ -6117,6 +6744,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr" s="6">
@@ -6164,6 +6796,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr" s="6">
@@ -6211,6 +6848,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr" s="6">
@@ -6258,6 +6900,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr" s="6">
@@ -6305,6 +6952,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr" s="6">
@@ -6352,6 +7004,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J131" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr" s="6">
@@ -6399,6 +7056,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J132" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr" s="6">
@@ -6446,6 +7108,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J133" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr" s="6">
@@ -6493,6 +7160,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J134" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr" s="6">
@@ -6540,6 +7212,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J135" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr" s="5">
@@ -6587,6 +7264,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J136" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr" s="5">
@@ -6634,6 +7316,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr" s="5">
@@ -6681,6 +7368,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J138" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr" s="5">
@@ -6728,6 +7420,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J139" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr" s="5">
@@ -6775,6 +7472,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J140" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr" s="5">
@@ -6822,6 +7524,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr" s="5">
@@ -6869,6 +7576,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J142" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr" s="5">
@@ -6916,6 +7628,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J143" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr" s="5">
@@ -6963,6 +7680,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr" s="6">
@@ -7010,6 +7732,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr" s="6">
@@ -7057,6 +7784,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr" s="6">
@@ -7104,6 +7836,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J147" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr" s="6">
@@ -7151,6 +7888,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J148" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr" s="5">
@@ -7198,6 +7940,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J149" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr" s="5">
@@ -7245,6 +7992,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr" s="5">
@@ -7292,6 +8044,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J151" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr" s="5">
@@ -7339,6 +8096,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J152" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr" s="5">
@@ -7386,6 +8148,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J153" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr" s="5">
@@ -7433,6 +8200,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J154" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr" s="5">
@@ -7480,6 +8252,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J155" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr" s="5">
@@ -7527,6 +8304,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J156" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr" s="5">
@@ -7574,6 +8356,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J157" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr" s="5">
@@ -7621,6 +8408,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J158" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr" s="5">
@@ -7668,6 +8460,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J159" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr" s="5">
@@ -7715,6 +8512,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr" s="5">
@@ -7762,6 +8564,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J161" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr" s="5">
@@ -7809,6 +8616,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J162" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr" s="5">
@@ -7856,6 +8668,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J163" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr" s="5">
@@ -7903,6 +8720,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J164" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr" s="5">
@@ -7950,6 +8772,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J165" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr" s="5">
@@ -7997,6 +8824,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J166" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr" s="5">
@@ -8044,6 +8876,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J167" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr" s="5">
@@ -8091,6 +8928,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J168" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr" s="5">
@@ -8138,6 +8980,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr" s="5">
@@ -8185,6 +9032,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J170" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr" s="5">
@@ -8232,6 +9084,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J171" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr" s="5">
@@ -8279,6 +9136,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J172" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr" s="5">
@@ -8326,6 +9188,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J173" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr" s="5">
@@ -8373,6 +9240,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J174" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr" s="5">
@@ -8420,6 +9292,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J175" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr" s="5">
@@ -8467,6 +9344,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J176" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr" s="5">
@@ -8514,6 +9396,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J177" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr" s="5">
@@ -8561,6 +9448,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J178" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr" s="5">
@@ -8608,6 +9500,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr" s="5">
@@ -8655,6 +9552,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J180" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr" s="5">
@@ -8702,6 +9604,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J181" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr" s="5">
@@ -8749,6 +9656,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J182" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr" s="5">
@@ -8796,6 +9708,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr" s="5">
@@ -8843,6 +9760,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J184" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr" s="5">
@@ -8890,6 +9812,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J185" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr" s="5">
@@ -8937,6 +9864,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J186" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr" s="5">
@@ -8984,6 +9916,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J187" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr" s="5">
@@ -9031,6 +9968,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J188" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr" s="5">
@@ -9078,6 +10020,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J189" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr" s="5">
@@ -9125,6 +10072,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J190" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr" s="5">
@@ -9172,6 +10124,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J191" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr" s="5">
@@ -9219,6 +10176,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J192" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr" s="5">
@@ -9266,6 +10228,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J193" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr" s="5">
@@ -9313,6 +10280,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J194" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr" s="5">
@@ -9360,6 +10332,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J195" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr" s="5">
@@ -9407,6 +10384,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J196" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr" s="5">
@@ -9454,6 +10436,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J197" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr" s="8">
@@ -9501,6 +10488,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J198" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr" s="8">
@@ -9548,6 +10540,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J199" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr" s="8">
@@ -9595,6 +10592,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J200" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr" s="8">
@@ -9642,6 +10644,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J201" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr" s="8">
@@ -9689,6 +10696,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J202" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr" s="8">
@@ -9736,6 +10748,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J203" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr" s="8">
@@ -9783,6 +10800,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J204" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr" s="8">
@@ -9830,6 +10852,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J205" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr" s="8">
@@ -9877,6 +10904,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J206" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr" s="8">
@@ -9924,6 +10956,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J207" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr" s="6">
@@ -9971,6 +11008,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J208" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr" s="6">
@@ -10018,6 +11060,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J209" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr" s="6">
@@ -10065,6 +11112,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J210" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr" s="6">
@@ -10112,6 +11164,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J211" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr" s="6">
@@ -10159,6 +11216,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J212" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr" s="6">
@@ -10206,6 +11268,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J213" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr" s="6">
@@ -10253,6 +11320,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J214" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr" s="6">
@@ -10300,6 +11372,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J215" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr" s="6">
@@ -10347,6 +11424,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J216" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr" s="6">
@@ -10394,6 +11476,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J217" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr" s="6">
@@ -10441,6 +11528,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J218" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr" s="6">
@@ -10488,6 +11580,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J219" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr" s="5">
@@ -10535,6 +11632,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J220" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr" s="5">
@@ -10582,6 +11684,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J221" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr" s="5">
@@ -10629,6 +11736,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J222" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr" s="5">
@@ -10676,6 +11788,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J223" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr" s="5">
@@ -10723,6 +11840,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J224" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr" s="5">
@@ -10770,6 +11892,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J225" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr" s="5">
@@ -10817,6 +11944,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J226" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr" s="5">
@@ -10864,6 +11996,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J227" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr" s="5">
@@ -10911,6 +12048,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J228" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr" s="5">
@@ -10958,6 +12100,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J229" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr" s="5">
@@ -11005,6 +12152,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J230" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr" s="5">
@@ -11052,6 +12204,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J231" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr" s="5">
@@ -11099,6 +12256,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J232" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr" s="5">
@@ -11146,6 +12308,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J233" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr" s="5">
@@ -11193,6 +12360,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J234" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr" s="5">
@@ -11240,6 +12412,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J235" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr" s="5">
@@ -11287,6 +12464,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J236" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr" s="5">
@@ -11334,6 +12516,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J237" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr" s="5">
@@ -11381,6 +12568,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J238" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr" s="5">
@@ -11428,6 +12620,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J239" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr" s="7">
@@ -11475,6 +12672,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J240" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr" s="7">
@@ -11522,6 +12724,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J241" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr" s="7">
@@ -11569,6 +12776,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J242" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr" s="7">
@@ -11616,6 +12828,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J243" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr" s="7">
@@ -11663,6 +12880,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J244" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr" s="7">
@@ -11710,6 +12932,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J245" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr" s="7">
@@ -11757,6 +12984,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J246" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr" s="7">
@@ -11804,6 +13036,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J247" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr" s="7">
@@ -11851,6 +13088,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J248" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr" s="7">
@@ -11898,6 +13140,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J249" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr" s="7">
@@ -11945,6 +13192,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J250" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr" s="7">
@@ -11992,6 +13244,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J251" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr" s="7">
@@ -12039,6 +13296,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J252" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr" s="7">
@@ -12086,6 +13348,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J253" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr" s="7">
@@ -12133,6 +13400,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J254" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr" s="7">
@@ -12180,6 +13452,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J255" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr" s="7">
@@ -12227,6 +13504,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J256" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr" s="7">
@@ -12274,6 +13556,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J257" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr" s="7">
@@ -12321,6 +13608,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J258" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr" s="7">
@@ -12368,6 +13660,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J259" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr" s="7">
@@ -12415,6 +13712,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J260" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr" s="7">
@@ -12462,6 +13764,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J261" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr" s="7">
@@ -12509,6 +13816,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J262" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr" s="7">
@@ -12556,6 +13868,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J263" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr" s="7">
@@ -12603,6 +13920,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J264" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr" s="7">
@@ -12650,6 +13972,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J265" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr" s="7">
@@ -12697,6 +14024,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J266" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr" s="7">
@@ -12744,6 +14076,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J267" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr" s="7">
@@ -12791,6 +14128,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J268" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr" s="7">
@@ -12838,6 +14180,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J269" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr" s="7">
@@ -12885,6 +14232,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J270" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr" s="7">
@@ -12932,6 +14284,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J271" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr" s="7">
@@ -12979,6 +14336,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J272" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr" s="7">
@@ -13026,6 +14388,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J273" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr" s="7">
@@ -13073,6 +14440,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J274" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr" s="7">
@@ -13120,6 +14492,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J275" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr" s="7">
@@ -13167,6 +14544,11 @@
           <t>Parameterized</t>
         </is>
       </c>
+      <c r="J276" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr" s="7">
@@ -13214,6 +14596,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J277" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr" s="7">
@@ -13261,6 +14648,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J278" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr" s="7">
@@ -13308,6 +14700,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J279" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr" s="7">
@@ -13355,6 +14752,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J280" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr" s="7">
@@ -13402,6 +14804,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J281" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr" s="7">
@@ -13449,6 +14856,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J282" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr" s="7">
@@ -13496,6 +14908,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J283" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr" s="7">
@@ -13543,6 +14960,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J284" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr" s="7">
@@ -13590,6 +15012,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J285" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr" s="7">
@@ -13637,6 +15064,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J286" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr" s="7">
@@ -13684,6 +15116,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J287" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr" s="7">
@@ -13731,6 +15168,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J288" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr" s="7">
@@ -13778,6 +15220,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J289" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr" s="7">
@@ -13825,6 +15272,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J290" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr" s="7">
@@ -13872,6 +15324,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J291" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr" s="7">
@@ -13919,6 +15376,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J292" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr" s="7">
@@ -13966,6 +15428,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J293" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr" s="7">
@@ -14013,6 +15480,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J294" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr" s="7">
@@ -14060,6 +15532,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J295" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr" s="7">
@@ -14107,6 +15584,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J296" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr" s="7">
@@ -14154,6 +15636,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J297" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr" s="7">
@@ -14201,6 +15688,11 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J298" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr" s="7">
@@ -14248,8 +15740,5733 @@
           <t>Test</t>
         </is>
       </c>
+      <c r="J299" t="inlineStr" s="2">
+        <is>
+          <t>Java/Selenium</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="0">
+        <is>
+          <t>User Login (API)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="0">
+        <is>
+          <t>valid credentials return 200 with a JWT token and user object</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="0">
+        <is>
+          <t>User Login (API)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="0">
+        <is>
+          <t>wrong password returns INVALID_CREDENTIALS</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="0">
+        <is>
+          <t>User Login (API)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="0">
+        <is>
+          <t>unknown email returns INVALID_CREDENTIALS</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="0">
+        <is>
+          <t>User Login (API)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="0">
+        <is>
+          <t>empty body returns VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (API)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="0">
+        <is>
+          <t>valid registration returns 201 with a JWT token and user object</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (API)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="0">
+        <is>
+          <t>duplicate email returns DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (API)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="0">
+        <is>
+          <t>missing first name returns VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (API)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="0">
+        <is>
+          <t>missing last name returns VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (API)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="0">
+        <is>
+          <t>missing email returns VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (API)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="0">
+        <is>
+          <t>missing password returns VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (API)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="0">
+        <is>
+          <t>weak password returns VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="0">
+        <is>
+          <t>F4.2; F4.3; F4.8</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="0">
+        <is>
+          <t>Booking Creation (API)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="0">
+        <is>
+          <t>booking-creation.spec</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="0">
+        <is>
+          <t>creates a booking with PENDING status and returns all required fields</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="0">
+        <is>
+          <t>F4.2; F4.3; F4.8</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="0">
+        <is>
+          <t>Booking Creation (API)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="0">
+        <is>
+          <t>booking-creation.spec</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="0">
+        <is>
+          <t>returns 401 when request is unauthenticated</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="0">
+        <is>
+          <t>F4.2; F4.3; F4.8</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="0">
+        <is>
+          <t>Booking Creation (API)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="0">
+        <is>
+          <t>booking-creation.spec</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="0">
+        <is>
+          <t>returns 409 when dates overlap with an existing booking</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="0">
+        <is>
+          <t>F4.2; F4.3; F4.8</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="0">
+        <is>
+          <t>Booking Creation (API)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="0">
+        <is>
+          <t>booking-creation.spec</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="0">
+        <is>
+          <t>returns 400 when numGuests exceeds property max guests</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="0">
+        <is>
+          <t>F4.2; F4.3; F4.8</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="0">
+        <is>
+          <t>Booking Creation (API)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="0">
+        <is>
+          <t>booking-creation.spec</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="0">
+        <is>
+          <t>returns 400 when checkIn date is in the past</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="0">
+        <is>
+          <t>F4.2; F4.3; F4.8</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="0">
+        <is>
+          <t>Booking Creation (API)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="0">
+        <is>
+          <t>booking-creation.spec</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="0">
+        <is>
+          <t>host receives a BOOKING_REQUEST notification after booking</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="0">
+        <is>
+          <t>F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="0">
+        <is>
+          <t>Host Booking Requests (API)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="0">
+        <is>
+          <t>booking-requests.spec</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="0">
+        <is>
+          <t>returns 403 for a non-host user</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="0">
+        <is>
+          <t>F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="0">
+        <is>
+          <t>Host Booking Requests (API)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="0">
+        <is>
+          <t>booking-requests.spec</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="0">
+        <is>
+          <t>confirms a PENDING booking</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="0">
+        <is>
+          <t>F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="0">
+        <is>
+          <t>Host Booking Requests (API)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="0">
+        <is>
+          <t>booking-requests.spec</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="0">
+        <is>
+          <t>returns 403 when a non-host attempts to confirm</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="0">
+        <is>
+          <t>F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="0">
+        <is>
+          <t>Host Booking Requests (API)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="0">
+        <is>
+          <t>booking-requests.spec</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="0">
+        <is>
+          <t>guest receives a BOOKING_CONFIRMED notification after host confirms</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="0">
+        <is>
+          <t>F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="0">
+        <is>
+          <t>Host Booking Requests (API)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="0">
+        <is>
+          <t>booking-requests.spec</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="0">
+        <is>
+          <t>declines a PENDING booking</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="0">
+        <is>
+          <t>F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="0">
+        <is>
+          <t>Host Booking Requests (API)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="0">
+        <is>
+          <t>booking-requests.spec</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="0">
+        <is>
+          <t>returns 403 when a non-host attempts to decline</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="0">
+        <is>
+          <t>F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="0">
+        <is>
+          <t>Host Booking Requests (API)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="0">
+        <is>
+          <t>booking-requests.spec</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="0">
+        <is>
+          <t>guest receives a BOOKING_DECLINED notification after host declines</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="0">
+        <is>
+          <t>F4.4; F4.5; F4.6; F4.8</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="0">
+        <is>
+          <t>Guest Bookings (API)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="0">
+        <is>
+          <t>mybooking.spec</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="0">
+        <is>
+          <t>returns pending bookings with pagination</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="0">
+        <is>
+          <t>F4.4; F4.5; F4.6; F4.8</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="0">
+        <is>
+          <t>Guest Bookings (API)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="0">
+        <is>
+          <t>mybooking.spec</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="0">
+        <is>
+          <t>returns full booking detail for a valid booking</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="0">
+        <is>
+          <t>F4.4; F4.5; F4.6; F4.8</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="0">
+        <is>
+          <t>Guest Bookings (API)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="0">
+        <is>
+          <t>mybooking.spec</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="0">
+        <is>
+          <t>returns 403 when booking belongs to another user</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="0">
+        <is>
+          <t>F4.4; F4.5; F4.6; F4.8</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="0">
+        <is>
+          <t>Guest Bookings (API)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="0">
+        <is>
+          <t>mybooking.spec</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="0">
+        <is>
+          <t>cancels a PENDING booking</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="0">
+        <is>
+          <t>F4.4; F4.5; F4.6; F4.8</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="0">
+        <is>
+          <t>Guest Bookings (API)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="0">
+        <is>
+          <t>mybooking.spec</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="0">
+        <is>
+          <t>returns 403 when a different user attempts the cancellation</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="0">
+        <is>
+          <t>F4.4; F4.5; F4.6; F4.8</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="0">
+        <is>
+          <t>Guest Bookings (API)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="0">
+        <is>
+          <t>mybooking.spec</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="0">
+        <is>
+          <t>host receives a BOOKING_CANCELLED notification after guest cancels</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr" s="0">
+        <is>
+          <t>F5.5; F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="0">
+        <is>
+          <t>Messaging (API)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr" s="0">
+        <is>
+          <t>messages.spec</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr" s="0">
+        <is>
+          <t>guest sends a message to host with a propertyId and receives 201</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr" s="0">
+        <is>
+          <t>F5.5; F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr" s="0">
+        <is>
+          <t>Messaging (API)</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr" s="0">
+        <is>
+          <t>messages.spec</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr" s="0">
+        <is>
+          <t>returns 400 when content is empty</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="0">
+        <is>
+          <t>F5.5; F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="0">
+        <is>
+          <t>Messaging (API)</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="0">
+        <is>
+          <t>messages.spec</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr" s="0">
+        <is>
+          <t>returns 400 when sender and receiver are the same user</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="0">
+        <is>
+          <t>F5.5; F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="0">
+        <is>
+          <t>Messaging (API)</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="0">
+        <is>
+          <t>messages.spec</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr" s="0">
+        <is>
+          <t>returns 200 with correct conversation shape</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="0">
+        <is>
+          <t>F5.5; F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="0">
+        <is>
+          <t>Messaging (API)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="0">
+        <is>
+          <t>messages.spec</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr" s="0">
+        <is>
+          <t>marks conversation as read and unread count drops to 0</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="0">
+        <is>
+          <t>F5.5; F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="0">
+        <is>
+          <t>Messaging (API)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="0">
+        <is>
+          <t>messages.spec</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr" s="0">
+        <is>
+          <t>returns 403 when a non-participant tries to mark a conversation as read</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 4, 5</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="0">
+        <is>
+          <t>F4.8; F5.8</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="0">
+        <is>
+          <t>Notifications (API)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="0">
+        <is>
+          <t>notifications.spec</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr" s="0">
+        <is>
+          <t>returns 200 with a notifications list and unreadCount</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 4, 5</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="0">
+        <is>
+          <t>F4.8; F5.8</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="0">
+        <is>
+          <t>Notifications (API)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="0">
+        <is>
+          <t>notifications.spec</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr" s="0">
+        <is>
+          <t>returns only unread notifications when unreadOnly=true</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 4, 5</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="0">
+        <is>
+          <t>F4.8; F5.8</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="0">
+        <is>
+          <t>Notifications (API)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="0">
+        <is>
+          <t>notifications.spec</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr" s="0">
+        <is>
+          <t>flips is_read to true for a valid notification ID</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 4, 5</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="0">
+        <is>
+          <t>F4.8; F5.8</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="0">
+        <is>
+          <t>Notifications (API)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="0">
+        <is>
+          <t>notifications.spec</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr" s="0">
+        <is>
+          <t>returns 404 for a non-existent notification ID</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 4, 5</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="0">
+        <is>
+          <t>F4.8; F5.8</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="0">
+        <is>
+          <t>Notifications (API)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="0">
+        <is>
+          <t>notifications.spec</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr" s="0">
+        <is>
+          <t>marks all as read then GET returns unreadCount 0</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 4, 5</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr" s="0">
+        <is>
+          <t>F4.8; F5.8</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="0">
+        <is>
+          <t>Notifications (API)</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr" s="0">
+        <is>
+          <t>notifications.spec</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr" s="0">
+        <is>
+          <t>returns 401 for an unauthenticated mark-all-as-read request</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr" s="0">
+        <is>
+          <t>F5.1; F5.2</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr" s="0">
+        <is>
+          <t>Reviews (API)</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr" s="0">
+        <is>
+          <t>reviews.spec</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr" s="0">
+        <is>
+          <t>guest submits a valid GUEST_TO_PROPERTY review and receives 201</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr" s="10">
+        <is>
+          <t>Fixme</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr" s="0">
+        <is>
+          <t>F5.1; F5.2</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr" s="0">
+        <is>
+          <t>Reviews (API)</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr" s="0">
+        <is>
+          <t>reviews.spec</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr" s="0">
+        <is>
+          <t>host submits a valid HOST_TO_GUEST review and receives 201</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr" s="10">
+        <is>
+          <t>Fixme</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr" s="0">
+        <is>
+          <t>F5.1; F5.2</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr" s="0">
+        <is>
+          <t>Reviews (API)</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr" s="0">
+        <is>
+          <t>reviews.spec</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr" s="0">
+        <is>
+          <t>returns 409 when a review already exists for the same booking and type</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr" s="10">
+        <is>
+          <t>Fixme</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr" s="0">
+        <is>
+          <t>F5.1; F5.2</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr" s="0">
+        <is>
+          <t>Reviews (API)</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr" s="0">
+        <is>
+          <t>reviews.spec</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr" s="0">
+        <is>
+          <t>returns 400 for a rating of 0 (below valid range)</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr" s="10">
+        <is>
+          <t>Fixme</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr" s="0">
+        <is>
+          <t>F5.1; F5.2</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="0">
+        <is>
+          <t>Reviews (API)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr" s="0">
+        <is>
+          <t>reviews.spec</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr" s="0">
+        <is>
+          <t>returns 400 for a rating of 6 (above valid range)</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr" s="10">
+        <is>
+          <t>Fixme</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr" s="0">
+        <is>
+          <t>F5.1; F5.2</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr" s="0">
+        <is>
+          <t>Reviews (API)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr" s="0">
+        <is>
+          <t>reviews.spec</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr" s="0">
+        <is>
+          <t>returns 403 when a non-participant submits a review</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr" s="2">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr" s="10">
+        <is>
+          <t>Fixme</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr" s="0">
+        <is>
+          <t>User Login (E2E)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr" s="0">
+        <is>
+          <t>session persists after browser restart</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr" s="0">
+        <is>
+          <t>User Login (E2E)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr" s="0">
+        <is>
+          <t>login stores token in localStorage</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr" s="0">
+        <is>
+          <t>User Login (E2E)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr" s="0">
+        <is>
+          <t>expired token logs the user out</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr" s="0">
+        <is>
+          <t>User Login (E2E)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr" s="0">
+        <is>
+          <t>successfully logging in redirects to homepage</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr" s="0">
+        <is>
+          <t>User Login (E2E)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr" s="0">
+        <is>
+          <t>invalid password should give error</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr" s="0">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr" s="0">
+        <is>
+          <t>User Login (E2E)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr" s="0">
+        <is>
+          <t>login.spec</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr" s="0">
+        <is>
+          <t>Email and password are required</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr" s="0">
+        <is>
+          <t>F1.3</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr" s="0">
+        <is>
+          <t>User Logout (E2E)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr" s="0">
+        <is>
+          <t>logout.spec</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr" s="0">
+        <is>
+          <t>logout shows logged-out UI</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr" s="0">
+        <is>
+          <t>F1.3</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr" s="0">
+        <is>
+          <t>User Logout (E2E)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr" s="0">
+        <is>
+          <t>logout.spec</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr" s="0">
+        <is>
+          <t>logout clears the token from localStorage</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr" s="0">
+        <is>
+          <t>F1.3</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr" s="0">
+        <is>
+          <t>User Logout (E2E)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr" s="0">
+        <is>
+          <t>logout.spec</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr" s="0">
+        <is>
+          <t>logout redirects to homepage</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr" s="0">
+        <is>
+          <t>F1.3</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr" s="0">
+        <is>
+          <t>User Logout (E2E)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr" s="0">
+        <is>
+          <t>logout.spec</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr" s="0">
+        <is>
+          <t>logged out user can visit login page</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr" s="0">
+        <is>
+          <t>F1.3</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr" s="0">
+        <is>
+          <t>User Logout (E2E)</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr" s="0">
+        <is>
+          <t>logout.spec</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr" s="0">
+        <is>
+          <t>user can log back in after logout</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr" s="0">
+        <is>
+          <t>successful registration redirects to homepage</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr" s="0">
+        <is>
+          <t>user is logged in after registration</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr" s="0">
+        <is>
+          <t>first name is required</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr" s="0">
+        <is>
+          <t>last name is required</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr" s="0">
+        <is>
+          <t>email is required</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr" s="0">
+        <is>
+          <t>password is required</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr" s="0">
+        <is>
+          <t>mismatched passwords show error</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr" s="0">
+        <is>
+          <t>password shorter than 8 characters is rejected</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr" s="5">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr" s="0">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr" s="0">
+        <is>
+          <t>User Registration (E2E)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr" s="0">
+        <is>
+          <t>register.spec</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr" s="0">
+        <is>
+          <t>registering with an existing email shows error</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr" s="0">
+        <is>
+          <t>Reserving a valid property appears in upcoming bookings</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr" s="0">
+        <is>
+          <t>Cancelling a reservation moves it to the cancelled tab</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr" s="0">
+        <is>
+          <t>Pending booking request is visible to the host</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr" s="0">
+        <is>
+          <t>Host confirming a booking moves it to the Confirmed tab</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr" s="0">
+        <is>
+          <t>Guest's booking shows CONFIRMED status in upcoming after host confirms</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr" s="0">
+        <is>
+          <t>Host declining a booking removes it from the pending tab</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr" s="0">
+        <is>
+          <t>Guest's booking shows DECLINED status after host declines</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr" s="0">
+        <is>
+          <t>Reserving a property notifies the host</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr" s="0">
+        <is>
+          <t>Cancelling a reservation notifies the host</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr" s="0">
+        <is>
+          <t>Host confirming a booking notifies the guest</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr" s="0">
+        <is>
+          <t>F4.3; F4.6; F4.7; F4.8</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr" s="0">
+        <is>
+          <t>Booking Flow (E2E)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr" s="0">
+        <is>
+          <t>booking.spec</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr" s="0">
+        <is>
+          <t>Host declining a booking notifies the guest</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr" s="0">
+        <is>
+          <t>F4.1</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr" s="0">
+        <is>
+          <t>Booking Widget (E2E)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr" s="0">
+        <is>
+          <t>widget.spec</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr" s="0">
+        <is>
+          <t>Booking widget is displayed</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr" s="0">
+        <is>
+          <t>F4.1</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr" s="0">
+        <is>
+          <t>Booking Widget (E2E)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr" s="0">
+        <is>
+          <t>widget.spec</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr" s="0">
+        <is>
+          <t>Price breakdown is displayed after valid checkin and checkout dates are selected</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr" s="0">
+        <is>
+          <t>F4.1</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr" s="0">
+        <is>
+          <t>Booking Widget (E2E)</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr" s="0">
+        <is>
+          <t>widget.spec</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr" s="0">
+        <is>
+          <t>Increment button is disabled after reaching property's max guest capacity</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr" s="8">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr" s="0">
+        <is>
+          <t>F4.1</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr" s="0">
+        <is>
+          <t>Booking Widget (E2E)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr" s="0">
+        <is>
+          <t>widget.spec</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr" s="0">
+        <is>
+          <t>Clicking reserve without authentication redirects to login</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr" s="0">
+        <is>
+          <t>F5.5</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr" s="0">
+        <is>
+          <t>Send Message (E2E)</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr" s="0">
+        <is>
+          <t>message.spec</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr" s="0">
+        <is>
+          <t>guest sending a message from property details page appears in guest messages page</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr" s="0">
+        <is>
+          <t>F5.5</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr" s="0">
+        <is>
+          <t>Send Message (E2E)</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr" s="0">
+        <is>
+          <t>message.spec</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr" s="0">
+        <is>
+          <t>guest sending a message from property details page appears in host messages page</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr" s="0">
+        <is>
+          <t>F5.5</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr" s="0">
+        <is>
+          <t>Send Message (E2E)</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr" s="0">
+        <is>
+          <t>message.spec</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr" s="0">
+        <is>
+          <t>guest sending a message from messages page appears in host messages page</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr" s="0">
+        <is>
+          <t>conversation list is displayed</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr" s="0">
+        <is>
+          <t>each conversation shows the other user name</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr" s="0">
+        <is>
+          <t>each conversation shows last message preview</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr" s="0">
+        <is>
+          <t>each conversation shows the related property name</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr" s="0">
+        <is>
+          <t>each conversation shows a timestamp</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr" s="0">
+        <is>
+          <t>clicking a conversation opens the thread</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr" s="0">
+        <is>
+          <t>thread header shows the other user name</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr" s="0">
+        <is>
+          <t>thread header shows the related property</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr" s="0">
+        <is>
+          <t>sent messages are displayed in the thread</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr" s="0">
+        <is>
+          <t>received messages are displayed in the thread</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr" s="0">
+        <is>
+          <t>each message shows text and timestamp</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr" s="0">
+        <is>
+          <t>thread auto-scrolls to the newest message</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr" s="0">
+        <is>
+          <t>F5.6; F5.7</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr" s="0">
+        <is>
+          <t>Messages Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr" s="0">
+        <is>
+          <t>messages-page.spec</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr" s="0">
+        <is>
+          <t>shows empty state when user has no conversations</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr" s="0">
+        <is>
+          <t>Notification Bell (E2E)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr" s="0">
+        <is>
+          <t>notification-bell.spec</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr" s="0">
+        <is>
+          <t>bell icon is visible when logged in</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr" s="0">
+        <is>
+          <t>Notification Bell (E2E)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr" s="0">
+        <is>
+          <t>notification-bell.spec</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr" s="0">
+        <is>
+          <t>bell badge shows unread count when user has unread notifications</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr" s="0">
+        <is>
+          <t>Notification Bell (E2E)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr" s="0">
+        <is>
+          <t>notification-bell.spec</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr" s="0">
+        <is>
+          <t>badge is hidden when user has no unread notifications</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr" s="0">
+        <is>
+          <t>Notification Bell (E2E)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr" s="0">
+        <is>
+          <t>notification-bell.spec</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr" s="0">
+        <is>
+          <t>bell is not visible when logged out</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr" s="0">
+        <is>
+          <t>Notifications Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr" s="0">
+        <is>
+          <t>notifications-page.spec</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr" s="0">
+        <is>
+          <t>unread notifications show the unread indicator</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr" s="0">
+        <is>
+          <t>Notifications Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr" s="0">
+        <is>
+          <t>notifications-page.spec</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr" s="0">
+        <is>
+          <t>clicking a message notification navigates to messages</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr" s="0">
+        <is>
+          <t>Notifications Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr" s="0">
+        <is>
+          <t>notifications-page.spec</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr" s="0">
+        <is>
+          <t>mark all as read clears all unread cards</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr" s="0">
+        <is>
+          <t>Notifications Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr" s="0">
+        <is>
+          <t>notifications-page.spec</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr" s="0">
+        <is>
+          <t>bell badge disappears after marking all as read</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr" s="0">
+        <is>
+          <t>Notifications Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr" s="0">
+        <is>
+          <t>notifications-page.spec</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr" s="0">
+        <is>
+          <t>read notifications do not show the unread indicator</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr" s="0">
+        <is>
+          <t>Notifications Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr" s="0">
+        <is>
+          <t>notifications-page.spec</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr" s="0">
+        <is>
+          <t>shows empty state when user has no notifications</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr" s="0">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr" s="0">
+        <is>
+          <t>F5.8</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr" s="0">
+        <is>
+          <t>Notifications Page (E2E)</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr" s="0">
+        <is>
+          <t>notifications-page.spec</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr" s="9">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr" s="0">
+        <is>
+          <t>redirects to login when not authenticated</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr" s="3">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr" s="10">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr" s="10">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr" s="3">
+        <is>
+          <t>TS/Playwright</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I299"/>
+  <autoFilter ref="A1:J409"/>
 </worksheet>
 </file>